--- a/DateBase/orders/Nhat 48_2026-7-21.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-21.xlsx
@@ -707,6 +707,9 @@
       <c r="G2" t="str">
         <v>0336751555515553551555571235335</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
